--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR VELOCIDADE.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR VELOCIDADE.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SENSOR VELOC IRON TITAN CG FAN150 2014 A 2015 189044</t>
+          <t>SENSOR VELOCIDADE  IRON TITAN CG FAN150 2014 A 2015 189044</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SENSOR VELOC IRON YS250 FAZER/ LANDER XTZ250/ TENERE/ LANDER ABS 189036</t>
+          <t>SENSOR VELOCIDADE  IRON YS250 FAZER/ LANDER XTZ250/ TENERE/ LANDER ABS 189036</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -482,7 +482,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -495,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SENSOR VELOC IRON YBR125I 2017 A 2019/ FACTOR150 2016 A 2019/ XTZ150/ FAZER150 189034</t>
+          <t>SENSOR VELOCIDADE  IRON YBR125I 2017 A 2019/ FACTOR150 2016 A 2019/ XTZ150/ FAZER150 189034</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SENSOR VELOC IRON CB500F/ CBR500/ CB500/ PCX150 189032</t>
+          <t>SENSOR VELOCIDADE  IRON CB500F/ CBR500/ CB500/ PCX150 189032</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,7 +549,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SENSOR VELOC CONDOR NXR150-160/ XRE190 2016 1102119</t>
+          <t>SENSOR VELOCIDADE  CONDOR NXR150-160/ XRE190 2016 1102119</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -553,7 +557,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +574,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SENSOR VELOC MHX TITAN FAN160 2014 A 2015/ FAN125 2014 A 2015</t>
+          <t>SENSOR VELOCIDADE  MHX TITAN FAN160 2014 A 2015/ FAN125 2014 A 2015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR VELOCIDADE.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR VELOCIDADE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -580,11 +550,6 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
     </row>
